--- a/HI02H11_L03_S02/VO_Manifest_Review3.xlsx
+++ b/HI02H11_L03_S02/VO_Manifest_Review3.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,7 +44,12 @@
       <name val="Nirmala UI"/>
       <i val="1"/>
       <color rgb="00808080"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Nirmala UI"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -91,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -103,6 +108,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -470,13 +478,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,29 +497,41 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Script (नई — यही बोलनी है)</t>
+          <t>नया / दोबारा</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Script — यही बोलनी है</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>अभी जो बोली जाती है</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>कहाँ</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>क्यों बदलनी है</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>G3 और G4 — इनकी मदद वाली lines बाक़ी slides जैसी नहीं हैं</t>
+          <t>G3 — बकरी वाली slide</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -519,17 +541,27 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>नया id</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
           <t>सोचिए बकरी मेले में किसके साथ आई थी?</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>फिर से कोशिश कीजिए, सही शब्द पहचानिए।   ← तस्वीरें दिखती हैं, शब्द नहीं</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>सही जोड़ी चुनिए (बकरी) — पहली मदद</t>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>फिर से कोशिश कीजिए, सही शब्द पहचानिए।</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>पहली मदद</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>अभी दोनों slides पर एक ही घिसी line आती है, और वो 'शब्द' कहती है जबकि वहाँ सिर्फ़ चित्र हैं</t>
         </is>
       </c>
     </row>
@@ -541,137 +573,211 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>दोबारा record</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>बकरी मेले में बकरे के साथ आई थी। बकरे के चित्र पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>यह बकरा है, बकरी-बकरे के साथ मेले में आई थी, इसपर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>सही जोड़ी चुनिए (बकरी) — दूसरी मदद</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>दूसरी मदद</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>सवाल बकरी का है पर line 'यह बकरा है' से शुरू होती है; बाक़ी slides का रूप अलग है</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>vo_h1_ghoda</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>सोचिए घोड़ा मेले में किसके साथ आया था?</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>फिर से कोशिश कीजिए, सही शब्द पहचानिए।   ← तस्वीरें दिखती हैं, शब्द नहीं</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>सही जोड़ी चुनिए (घोड़ा) — पहली मदद</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>G4 — घोड़ा वाली slide</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>vo_h1_ghoda</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>नया id</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>सोचिए घोड़ा मेले में किसके साथ आया था?</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>फिर से कोशिश कीजिए, सही शब्द पहचानिए।</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>पहली मदद</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>वही घिसी line, वही 'शब्द' वाली गड़बड़</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>vo_h2_ghoda</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>दोबारा record</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>घोड़ा मेले में घोड़ी के साथ आया था। घोड़ी के चित्र पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>यह घोड़ी है, घोड़ा-घोड़ी के साथ मेले में आया था, इसपर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>सही जोड़ी चुनिए (घोड़ा) — दूसरी मदद</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>दूसरी मदद</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>सवाल घोड़े का है पर line 'यह घोड़ी है' से शुरू होती है</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>सवाल वाली line — deck के ढाँचे पर लाने के लिए</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>vo_q_sherni</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>शेरनी मेले में किसके साथ आई थी?</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>यह शेरनी है, इसे इसकी सही जोड़ी से मिलाइए।</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>सही जोड़ी चुनिए (शेरनी)</t>
-        </is>
-      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>vo_q_mor</t>
+          <t>vo_q_sherni</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>मोर मेले में किसके साथ आया था?</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>यह मोर है, इसे इसकी सही जोड़ी से मिलाइए।</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>सही जोड़ी चुनिए (मोर)</t>
+          <t>दोबारा record</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>शेरनी मेले में किसके साथ आई थी?</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>यह शेरनी है, इसे इसकी सही जोड़ी से मिलाइए।</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>G1 का सवाल</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>deck बकरी/घोड़ा के लिए यही रूप लिखता है; ये तीन पुराने रूप में हैं</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>vo_q_mor</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>दोबारा record</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>मोर मेले में किसके साथ आया था?</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>यह मोर है, इसे इसकी सही जोड़ी से मिलाइए।</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>G2 का सवाल</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>वही</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
           <t>vo_q_bail</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>दोबारा record</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>बैल मेले में किसके साथ आया था?</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>यह बैल है, इसे इसकी सही जोड़ी से मिलाइए।</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>सही जोड़ी चुनिए (बैल)</t>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>P1 का सवाल</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>वही</t>
         </is>
       </c>
     </row>

--- a/HI02H11_L03_S02/VO_Manifest_Review3.xlsx
+++ b/HI02H11_L03_S02/VO_Manifest_Review3.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
+        <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F1"/>
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -478,15 +478,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,287 +496,87 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>नया / दोबारा</t>
+          <t>Script — यही बोलनी है</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Script — यही बोलनी है</t>
+          <t>अभी जो सुनाई देती है</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>अभी जो बोली जाती है</t>
+          <t>कहाँ</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>कहाँ</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>क्यों बदलनी है</t>
+          <t>टिप्पणी</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>G3 — बकरी वाली slide</t>
+          <t>दोबारा record करनी हैं — इनमें पुरानी बात बोली गई है</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>vo_h1_bakri</t>
+          <t>vo_q_bakri</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>नया id</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>सोचिए बकरी मेले में किसके साथ आई थी?</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>फिर से कोशिश कीजिए, सही शब्द पहचानिए।</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>पहली मदद</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>अभी दोनों slides पर एक ही घिसी line आती है, और वो 'शब्द' कहती है जबकि वहाँ सिर्फ़ चित्र हैं</t>
+          <t>बकरी मेले में किसके साथ आई थी?</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>यह किसके साथ मेले में आई थी?  (यही सुनाई देता है)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>G3 — बकरी वाली slide का सवाल</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>card में नई script लिखी है पर clip पुरानी बोलती है। batch 18 में आई थी।</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>vo_h2_bakri</t>
+          <t>vo_q_ghoda</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>दोबारा record</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>बकरी मेले में बकरे के साथ आई थी। बकरे के चित्र पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>यह बकरा है, बकरी-बकरे के साथ मेले में आई थी, इसपर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>दूसरी मदद</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>सवाल बकरी का है पर line 'यह बकरा है' से शुरू होती है; बाक़ी slides का रूप अलग है</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>G4 — घोड़ा वाली slide</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>vo_h1_ghoda</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>नया id</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>सोचिए घोड़ा मेले में किसके साथ आया था?</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>फिर से कोशिश कीजिए, सही शब्द पहचानिए।</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>पहली मदद</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>वही घिसी line, वही 'शब्द' वाली गड़बड़</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>vo_h2_ghoda</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>दोबारा record</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>घोड़ा मेले में घोड़ी के साथ आया था। घोड़ी के चित्र पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>यह घोड़ी है, घोड़ा-घोड़ी के साथ मेले में आया था, इसपर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>दूसरी मदद</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>सवाल घोड़े का है पर line 'यह घोड़ी है' से शुरू होती है</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>सवाल वाली line — deck के ढाँचे पर लाने के लिए</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>vo_q_sherni</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>दोबारा record</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>शेरनी मेले में किसके साथ आई थी?</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>यह शेरनी है, इसे इसकी सही जोड़ी से मिलाइए।</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>G1 का सवाल</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>deck बकरी/घोड़ा के लिए यही रूप लिखता है; ये तीन पुराने रूप में हैं</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>vo_q_mor</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>दोबारा record</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>मोर मेले में किसके साथ आया था?</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>यह मोर है, इसे इसकी सही जोड़ी से मिलाइए।</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>G2 का सवाल</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>वही</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>vo_q_bail</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>दोबारा record</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>बैल मेले में किसके साथ आया था?</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>यह बैल है, इसे इसकी सही जोड़ी से मिलाइए।</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>P1 का सवाल</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>वही</t>
+          <t>घोड़ा मेले में किसके साथ आया था?</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>यह किसके साथ मेले में आया था?  (सुनकर पक्का कीजिए)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>G4 — घोड़ा वाली slide का सवाल</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>बकरी की जुड़वाँ — उसी batch 18 से, और नई खेप में भी नहीं थी। शायद वही गड़बड़।</t>
         </is>
       </c>
     </row>
